--- a/diseases/d133/2026-2029.xlsx
+++ b/diseases/d133/2026-2029.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>51</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0.4765889018424507</v>
       </c>
@@ -3036,9 +3033,6 @@
       <c r="O14" t="n">
         <v>48</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0.4485542605576006</v>
       </c>
@@ -4932,9 +4926,6 @@
       <c r="O24" t="n">
         <v>47</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0.4392093801293172</v>
       </c>
@@ -6828,9 +6819,6 @@
       <c r="O34" t="n">
         <v>43</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0.4018298584161838</v>
       </c>
@@ -8724,9 +8712,6 @@
       <c r="O44" t="n">
         <v>45</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0.4205196192727506</v>
       </c>
@@ -10620,9 +10605,6 @@
       <c r="O54" t="n">
         <v>37</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0.01060064109124673</v>
       </c>
@@ -10995,9 +10977,6 @@
       <c r="O56" t="n">
         <v>35</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0.3270708149899171</v>
       </c>
@@ -11391,9 +11370,6 @@
       <c r="O58" t="n">
         <v>49</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0.01403868685056999</v>
       </c>
@@ -11766,9 +11742,6 @@
       <c r="O60" t="n">
         <v>49</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0.01403868685056999</v>
       </c>
@@ -12141,9 +12114,6 @@
       <c r="O62" t="n">
         <v>42</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0.01203316015763142</v>
       </c>
@@ -12516,9 +12486,6 @@
       <c r="O64" t="n">
         <v>23</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0.006589587705369587</v>
       </c>
@@ -12891,9 +12858,6 @@
       <c r="O66" t="n">
         <v>54</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0.5046235431273006</v>
       </c>
@@ -13287,9 +13251,6 @@
       <c r="O68" t="n">
         <v>96</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0.0275043660745861</v>
       </c>
@@ -13662,9 +13623,6 @@
       <c r="O70" t="n">
         <v>38</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0.01088714490452366</v>
       </c>
@@ -14037,9 +13995,6 @@
       <c r="O72" t="n">
         <v>55</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0.01575770973023162</v>
       </c>
@@ -14412,9 +14367,6 @@
       <c r="O74" t="n">
         <v>37</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0.01060064109124673</v>
       </c>
@@ -14787,9 +14739,6 @@
       <c r="O76" t="n">
         <v>101</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0.02893688514097079</v>
       </c>
@@ -15085,6 +15034,378 @@
         </is>
       </c>
       <c r="BC77" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>D133</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>carbapenemase-producing-organisms-surveillance</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Carbapenemase-producing organisms surveillance</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>D133</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Carbapenemase-producing organisms surveillance</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>产碳青霉烯酶微生物监测</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>48</v>
+      </c>
+      <c r="O78" t="n">
+        <v>48</v>
+      </c>
+      <c r="R78" t="n">
+        <v>0.01375218303729305</v>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP78" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR78" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS78" t="inlineStr"/>
+      <c r="AT78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV78" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA78" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB78" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC78" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>D133</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>carbapenemase-producing-organisms-surveillance</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Carbapenemase-producing organisms surveillance</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>D133</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Carbapenemase-producing organisms surveillance</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>产碳青霉烯酶微生物监测</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N79" t="n">
+        <v>48</v>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>SER_US_CPO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>SER_US_CPO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>Carbapenemase-Producing Organisms (CPO), Total</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>organism_detections</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD79" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE79" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF79" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG79" t="inlineStr">
+        <is>
+          <t>reported_aggregate</t>
+        </is>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>US_NNDSS_CPO_current</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>United States NNDSS broad CPO reports; the source label does not establish infection rather than colonization.</t>
+        </is>
+      </c>
+      <c r="AM79" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP79" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR79" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS79" t="inlineStr"/>
+      <c r="AT79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV79" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA79" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB79" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC79" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -15123,7 +15444,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -15206,7 +15527,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10">
@@ -15216,7 +15537,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11">
@@ -15236,7 +15557,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13">
@@ -15268,7 +15589,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2044</v>
+        <v>2092</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d133/2026-2029.xlsx
+++ b/diseases/d133/2026-2029.xlsx
@@ -15411,6 +15411,378 @@
         </is>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>D133</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>carbapenemase-producing-organisms-surveillance</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Carbapenemase-producing organisms surveillance</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>D133</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Carbapenemase-producing organisms surveillance</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>产碳青霉烯酶微生物监测</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>76</v>
+      </c>
+      <c r="O80" t="n">
+        <v>76</v>
+      </c>
+      <c r="R80" t="n">
+        <v>0.02177428980904733</v>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP80" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR80" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS80" t="inlineStr"/>
+      <c r="AT80" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV80" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA80" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB80" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC80" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>D133</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>carbapenemase-producing-organisms-surveillance</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Carbapenemase-producing organisms surveillance</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>D133</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Carbapenemase-producing organisms surveillance</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>产碳青霉烯酶微生物监测</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N81" t="n">
+        <v>76</v>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>SER_US_CPO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>SER_US_CPO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>Carbapenemase-Producing Organisms (CPO), Total</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>organism_detections</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD81" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE81" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF81" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG81" t="inlineStr">
+        <is>
+          <t>reported_aggregate</t>
+        </is>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI81" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>US_NNDSS_CPO_current</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>United States NNDSS broad CPO reports; the source label does not establish infection rather than colonization.</t>
+        </is>
+      </c>
+      <c r="AM81" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP81" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR81" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS81" t="inlineStr"/>
+      <c r="AT81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV81" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA81" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB81" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC81" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15444,7 +15816,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -15527,7 +15899,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10">
@@ -15537,7 +15909,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11">
@@ -15557,7 +15929,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13">
@@ -15589,7 +15961,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2092</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d133/2026-2029.xlsx
+++ b/diseases/d133/2026-2029.xlsx
@@ -15783,6 +15783,378 @@
         </is>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>D133</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>carbapenemase-producing-organisms-surveillance</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Carbapenemase-producing organisms surveillance</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>D133</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Carbapenemase-producing organisms surveillance</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>产碳青霉烯酶微生物监测</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N82" t="n">
+        <v>60</v>
+      </c>
+      <c r="O82" t="n">
+        <v>60</v>
+      </c>
+      <c r="R82" t="n">
+        <v>0.01719022879661631</v>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP82" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR82" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS82" t="inlineStr"/>
+      <c r="AT82" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV82" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA82" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB82" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC82" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>D133</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>carbapenemase-producing-organisms-surveillance</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Carbapenemase-producing organisms surveillance</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>D133</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Carbapenemase-producing organisms surveillance</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>产碳青霉烯酶微生物监测</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N83" t="n">
+        <v>60</v>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>SER_US_CPO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>SER_US_CPO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>Carbapenemase-Producing Organisms (CPO), Total</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>organism_detections</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD83" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE83" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF83" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG83" t="inlineStr">
+        <is>
+          <t>reported_aggregate</t>
+        </is>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI83" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>US_NNDSS_CPO_current</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>United States NNDSS broad CPO reports; the source label does not establish infection rather than colonization.</t>
+        </is>
+      </c>
+      <c r="AM83" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP83" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR83" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS83" t="inlineStr"/>
+      <c r="AT83" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV83" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA83" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB83" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC83" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15816,7 +16188,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -15899,7 +16271,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10">
@@ -15909,7 +16281,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11">
@@ -15929,7 +16301,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13">
@@ -15961,7 +16333,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2168</v>
+        <v>2228</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d133/2026-2029.xlsx
+++ b/diseases/d133/2026-2029.xlsx
@@ -16155,6 +16155,378 @@
         </is>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>D133</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>carbapenemase-producing-organisms-surveillance</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Carbapenemase-producing organisms surveillance</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>D133</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Carbapenemase-producing organisms surveillance</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>产碳青霉烯酶微生物监测</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N84" t="n">
+        <v>83</v>
+      </c>
+      <c r="O84" t="n">
+        <v>83</v>
+      </c>
+      <c r="R84" t="n">
+        <v>0.0237798165019859</v>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP84" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR84" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS84" t="inlineStr"/>
+      <c r="AT84" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV84" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA84" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB84" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC84" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>D133</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>carbapenemase-producing-organisms-surveillance</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Carbapenemase-producing organisms surveillance</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>D133</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Carbapenemase-producing organisms surveillance</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>产碳青霉烯酶微生物监测</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N85" t="n">
+        <v>83</v>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>SER_US_CPO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>SER_US_CPO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>Carbapenemase-Producing Organisms (CPO), Total</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>organism_detections</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD85" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE85" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF85" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG85" t="inlineStr">
+        <is>
+          <t>reported_aggregate</t>
+        </is>
+      </c>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI85" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>US_NNDSS_CPO_current</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>United States NNDSS broad CPO reports; the source label does not establish infection rather than colonization.</t>
+        </is>
+      </c>
+      <c r="AM85" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP85" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR85" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS85" t="inlineStr"/>
+      <c r="AT85" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV85" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA85" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB85" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC85" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16188,7 +16560,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -16271,7 +16643,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10">
@@ -16281,7 +16653,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="11">
@@ -16301,7 +16673,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13">
@@ -16333,7 +16705,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2228</v>
+        <v>2311</v>
       </c>
     </row>
     <row r="16">
